--- a/Retail_Purchase_Agreement_Blank.xlsx
+++ b/Retail_Purchase_Agreement_Blank.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,16 +33,20 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="9"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -65,17 +69,17 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="6.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="7"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="6.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
+      <sz val="6"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -83,11 +87,16 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <sz val="6.5"/>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
       <sz val="7.5"/>
     </font>
     <font>
@@ -97,12 +106,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <sz val="8"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -323,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -332,57 +341,60 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -391,98 +403,98 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -893,146 +905,146 @@
     <col width="7.1" customWidth="1" min="8" max="8"/>
     <col width="7.1" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="10.5" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="9.5" customWidth="1" min="12" max="12"/>
     <col width="1.2" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>EXCELLENT AUTO SALES AND LEASING</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>RETAIL PURCHASE AGREEMENT</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>6419 ALONDRA BLVD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="13" customHeight="1">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>PARAMOUNT, CA 90723</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>CUST#</t>
         </is>
       </c>
-      <c r="L1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>6419 ALONDRA BLVD</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Deal Number:</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="13" customHeight="1">
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>PARAMOUNT, CA 90723</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="n"/>
-      <c r="J3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Tel: (310)906-8117      Fax: (562)529-7997</t>
         </is>
       </c>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="9" t="n"/>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Deal Number:</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="n"/>
     </row>
     <row r="5" ht="6" customHeight="1">
       <c r="I5" s="8" t="n"/>
       <c r="J5" s="9" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Purchaser's Name(s):</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
       <c r="I6" s="8" t="n"/>
       <c r="J6" s="9" t="n"/>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n"/>
+      <c r="L6" s="7" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Address(es):</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
       <c r="I7" s="8" t="n"/>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>County:</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n"/>
+      <c r="L7" s="7" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Telephone (1):</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n"/>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="9" t="n"/>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>Telephone (2):</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n"/>
+      <c r="L8" s="7" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Email (1):</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>Email (2):</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n"/>
+      <c r="L9" s="7" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>The Odometer Reading for the Vehicle You are purchasing is accurate unless indicated otherwise. Please refer to the Odometer Mileage Statement for full disclosure.</t>
         </is>
@@ -1040,604 +1052,598 @@
     </row>
     <row r="11" ht="5" customHeight="1"/>
     <row r="12" ht="13" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>MAKE</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>MODEL</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>COLOR</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>STOCK NO.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="17" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="17" t="n"/>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>VIN</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>(Vehicle)</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>ODOMETER READING     ☐ Not Accurate</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>ODOMETER READING
+☐ Not Accurate</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>SALESPERSON</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="20" t="n"/>
-      <c r="I15" s="17" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>THE VEHICLE IS:      ☐ NEW      ☐ USED</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>THE VEHICLE IS:
+☐ NEW      ☐ USED</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>PRIOR USE DISCLOSURE:   ☐ DEMONSTRATOR   ☐ PREVIOUSLY LEASED   ☐ EXECUTIVE VEHICLE   ☐ RENTAL   ☐ OTHER ______</t>
         </is>
       </c>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="20" t="n"/>
-      <c r="I16" s="17" t="n"/>
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="18" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>WARRANTY STATEMENT</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="20" t="n"/>
-      <c r="I17" s="17" t="n"/>
-      <c r="K17" s="24" t="inlineStr">
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t>Base Selling Price</t>
         </is>
       </c>
-      <c r="L17" s="25" t="n"/>
+      <c r="L17" s="26" t="n"/>
     </row>
     <row r="18" ht="11" customHeight="1">
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>We are selling this Vehicle to You AS-IS and We expressly disclaim all warranties, express and implied, including any implied warranties of merchantability and fitness for a particular purpose, unless the box beside "Used Vehicle Limited Warranty Applies" is marked below or We enter into a service contract with You at the time of, or within 90 days of, the date of this transaction. All warranties, if any, by a manufacturer or supplier other than Our Dealership are theirs, not Ours, and no manufacturer or supplier shall be liable for performance under such warranties. We neither assume nor authorize any other person to assume for Us any liability in connection with the sale of the Vehicle and related goods and services.</t>
         </is>
       </c>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="27" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="K18" s="28" t="inlineStr">
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="K18" s="29" t="inlineStr">
         <is>
           <t>Optional Items:</t>
         </is>
       </c>
-      <c r="L18" s="29" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19" ht="11" customHeight="1">
       <c r="B19" s="8" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="30" t="n"/>
-      <c r="H19" s="30" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="31" t="n"/>
+      <c r="H19" s="31" t="n"/>
       <c r="I19" s="9" t="n"/>
-      <c r="K19" s="31" t="n"/>
-      <c r="L19" s="32" t="n"/>
+      <c r="K19" s="32" t="n"/>
+      <c r="L19" s="33" t="n"/>
     </row>
     <row r="20" ht="11" customHeight="1">
       <c r="B20" s="8" t="n"/>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="30" t="n"/>
-      <c r="G20" s="30" t="n"/>
-      <c r="H20" s="30" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="31" t="n"/>
       <c r="I20" s="9" t="n"/>
-      <c r="K20" s="31" t="n"/>
-      <c r="L20" s="32" t="n"/>
+      <c r="K20" s="32" t="n"/>
+      <c r="L20" s="33" t="n"/>
     </row>
     <row r="21" ht="11" customHeight="1">
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="30" t="n"/>
-      <c r="H21" s="30" t="n"/>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="31" t="n"/>
+      <c r="G21" s="31" t="n"/>
+      <c r="H21" s="31" t="n"/>
       <c r="I21" s="9" t="n"/>
-      <c r="K21" s="31" t="n"/>
-      <c r="L21" s="32" t="n"/>
+      <c r="K21" s="32" t="n"/>
+      <c r="L21" s="33" t="n"/>
     </row>
     <row r="22" ht="11" customHeight="1">
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="30" t="n"/>
-      <c r="G22" s="30" t="n"/>
-      <c r="H22" s="30" t="n"/>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="31" t="n"/>
+      <c r="H22" s="31" t="n"/>
       <c r="I22" s="9" t="n"/>
-      <c r="K22" s="31" t="n"/>
-      <c r="L22" s="32" t="n"/>
+      <c r="K22" s="32" t="n"/>
+      <c r="L22" s="33" t="n"/>
     </row>
     <row r="23" ht="11" customHeight="1">
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="30" t="n"/>
-      <c r="H23" s="30" t="n"/>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="31" t="n"/>
+      <c r="H23" s="31" t="n"/>
       <c r="I23" s="9" t="n"/>
-      <c r="K23" s="31" t="n"/>
-      <c r="L23" s="32" t="n"/>
+      <c r="K23" s="32" t="n"/>
+      <c r="L23" s="33" t="n"/>
     </row>
     <row r="24" ht="11" customHeight="1">
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="30" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="30" t="n"/>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="31" t="n"/>
       <c r="I24" s="9" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="32" t="n"/>
+      <c r="K24" s="32" t="n"/>
+      <c r="L24" s="33" t="n"/>
     </row>
     <row r="25" ht="11" customHeight="1">
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="33" t="n"/>
-      <c r="E25" s="33" t="n"/>
-      <c r="F25" s="33" t="n"/>
-      <c r="G25" s="33" t="n"/>
-      <c r="H25" s="33" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="32" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="34" t="n"/>
+      <c r="D25" s="34" t="n"/>
+      <c r="E25" s="34" t="n"/>
+      <c r="F25" s="34" t="n"/>
+      <c r="G25" s="34" t="n"/>
+      <c r="H25" s="34" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="K25" s="32" t="n"/>
+      <c r="L25" s="33" t="n"/>
     </row>
     <row r="26" ht="13" customHeight="1">
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>CONTRACTUAL DISCLOSURE STATEMENT (USED VEHICLES ONLY) The information</t>
         </is>
       </c>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="27" t="n"/>
-      <c r="H26" s="27" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="K26" s="31" t="n"/>
-      <c r="L26" s="32" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="K26" s="32" t="n"/>
+      <c r="L26" s="33" t="n"/>
     </row>
     <row r="27" ht="11" customHeight="1">
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>You see on the window form for this Vehicle is part of this contract. Information on the window form overrides any contrary provisions in the contract of sale.  Traducción española: Guía para compradores de vehículos usados. La información que ve en el formulario de la ventanilla para este vehículo forma parte del presente contrato. La información del formulario de la ventanilla deja sin efecto toda disposición en contrario contenida en el contrato de venta.</t>
         </is>
       </c>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="30" t="n"/>
-      <c r="G27" s="30" t="n"/>
-      <c r="H27" s="30" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="31" t="n"/>
+      <c r="H27" s="31" t="n"/>
       <c r="I27" s="9" t="n"/>
-      <c r="K27" s="31" t="n"/>
-      <c r="L27" s="32" t="n"/>
+      <c r="K27" s="32" t="n"/>
+      <c r="L27" s="33" t="n"/>
     </row>
     <row r="28" ht="11" customHeight="1">
       <c r="B28" s="8" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="30" t="n"/>
-      <c r="F28" s="30" t="n"/>
-      <c r="G28" s="30" t="n"/>
-      <c r="H28" s="30" t="n"/>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="31" t="n"/>
       <c r="I28" s="9" t="n"/>
-      <c r="K28" s="31" t="n"/>
-      <c r="L28" s="32" t="n"/>
+      <c r="K28" s="32" t="n"/>
+      <c r="L28" s="33" t="n"/>
     </row>
     <row r="29" ht="11" customHeight="1">
       <c r="B29" s="8" t="n"/>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="30" t="n"/>
-      <c r="H29" s="30" t="n"/>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="31" t="n"/>
+      <c r="H29" s="31" t="n"/>
       <c r="I29" s="9" t="n"/>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="32" t="n"/>
+      <c r="K29" s="32" t="n"/>
+      <c r="L29" s="33" t="n"/>
     </row>
     <row r="30" ht="11" customHeight="1">
       <c r="B30" s="8" t="n"/>
-      <c r="C30" s="30" t="n"/>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="30" t="n"/>
-      <c r="F30" s="30" t="n"/>
-      <c r="G30" s="30" t="n"/>
-      <c r="H30" s="30" t="n"/>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
       <c r="I30" s="9" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="32" t="n"/>
+      <c r="K30" s="32" t="n"/>
+      <c r="L30" s="33" t="n"/>
     </row>
     <row r="31" ht="11" customHeight="1">
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="33" t="n"/>
-      <c r="E31" s="33" t="n"/>
-      <c r="F31" s="33" t="n"/>
-      <c r="G31" s="33" t="n"/>
-      <c r="H31" s="33" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="32" t="n"/>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="34" t="n"/>
+      <c r="D31" s="34" t="n"/>
+      <c r="E31" s="34" t="n"/>
+      <c r="F31" s="34" t="n"/>
+      <c r="G31" s="34" t="n"/>
+      <c r="H31" s="34" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="K31" s="32" t="n"/>
+      <c r="L31" s="33" t="n"/>
     </row>
     <row r="32" ht="11" customHeight="1">
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>☐ Used Vehicle Limited Warranty Applies:  We are providing a Used Vehicle Limited Warranty in connection with this transaction. Any implied warranties apply for the duration of the Limited Warranty.</t>
         </is>
       </c>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="27" t="n"/>
-      <c r="H32" s="27" t="n"/>
-      <c r="I32" s="7" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="32" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="K32" s="32" t="n"/>
+      <c r="L32" s="33" t="n"/>
     </row>
     <row r="33" ht="11" customHeight="1">
       <c r="B33" s="8" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="30" t="n"/>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="30" t="n"/>
-      <c r="H33" s="30" t="n"/>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="31" t="n"/>
+      <c r="F33" s="31" t="n"/>
+      <c r="G33" s="31" t="n"/>
+      <c r="H33" s="31" t="n"/>
       <c r="I33" s="9" t="n"/>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="32" t="n"/>
+      <c r="K33" s="32" t="n"/>
+      <c r="L33" s="33" t="n"/>
     </row>
     <row r="34" ht="11" customHeight="1">
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="33" t="n"/>
-      <c r="E34" s="33" t="n"/>
-      <c r="F34" s="33" t="n"/>
-      <c r="G34" s="33" t="n"/>
-      <c r="H34" s="33" t="n"/>
-      <c r="I34" s="12" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="32" t="n"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="34" t="n"/>
+      <c r="D34" s="34" t="n"/>
+      <c r="E34" s="34" t="n"/>
+      <c r="F34" s="34" t="n"/>
+      <c r="G34" s="34" t="n"/>
+      <c r="H34" s="34" t="n"/>
+      <c r="I34" s="13" t="n"/>
+      <c r="K34" s="32" t="n"/>
+      <c r="L34" s="33" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
         <is>
           <t>TRADE VEHICLE INFORMATION</t>
         </is>
       </c>
-      <c r="C35" s="20" t="n"/>
-      <c r="D35" s="20" t="n"/>
-      <c r="E35" s="20" t="n"/>
-      <c r="F35" s="20" t="n"/>
-      <c r="G35" s="20" t="n"/>
-      <c r="H35" s="20" t="n"/>
-      <c r="I35" s="17" t="n"/>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="32" t="n"/>
-    </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="B36" s="36" t="inlineStr">
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="21" t="n"/>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="21" t="n"/>
+      <c r="H35" s="21" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="K35" s="32" t="n"/>
+      <c r="L35" s="33" t="n"/>
+    </row>
+    <row r="36" ht="12.5" customHeight="1">
+      <c r="B36" s="37" t="inlineStr">
         <is>
           <t>Lienholder Name:</t>
         </is>
       </c>
-      <c r="C36" s="37" t="n"/>
+      <c r="C36" s="28" t="n"/>
       <c r="D36" s="38" t="n"/>
-      <c r="E36" s="38" t="n"/>
-      <c r="F36" s="38" t="n"/>
-      <c r="G36" s="38" t="n"/>
-      <c r="H36" s="38" t="n"/>
-      <c r="I36" s="39" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="32" t="n"/>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="B37" s="40" t="inlineStr">
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="39" t="n"/>
+      <c r="H36" s="39" t="n"/>
+      <c r="I36" s="40" t="n"/>
+      <c r="K36" s="32" t="n"/>
+      <c r="L36" s="33" t="n"/>
+    </row>
+    <row r="37" ht="12.5" customHeight="1">
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>Lienholder Address:</t>
         </is>
       </c>
-      <c r="C37" s="41" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="42" t="n"/>
-      <c r="K37" s="31" t="n"/>
-      <c r="L37" s="32" t="n"/>
-    </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="B38" s="40" t="inlineStr">
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="42" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="43" t="n"/>
+      <c r="K37" s="32" t="n"/>
+      <c r="L37" s="33" t="n"/>
+    </row>
+    <row r="38" ht="12.5" customHeight="1">
+      <c r="B38" s="41" t="inlineStr">
         <is>
           <t>Year:</t>
         </is>
       </c>
-      <c r="C38" s="41" t="n"/>
-      <c r="D38" s="43" t="inlineStr">
+      <c r="C38" s="42" t="n"/>
+      <c r="D38" s="44" t="inlineStr">
         <is>
           <t>Make:</t>
         </is>
       </c>
-      <c r="E38" s="41" t="n"/>
-      <c r="F38" s="43" t="inlineStr">
+      <c r="E38" s="42" t="n"/>
+      <c r="F38" s="44" t="inlineStr">
         <is>
           <t>Model:</t>
         </is>
       </c>
-      <c r="G38" s="41" t="n"/>
-      <c r="H38" s="43" t="inlineStr">
+      <c r="G38" s="42" t="n"/>
+      <c r="H38" s="44" t="inlineStr">
         <is>
           <t>Color:</t>
         </is>
       </c>
-      <c r="I38" s="44" t="n"/>
-      <c r="K38" s="45" t="inlineStr">
+      <c r="I38" s="45" t="n"/>
+      <c r="K38" s="46" t="inlineStr">
         <is>
           <t>TOTAL SELLING PRICE</t>
         </is>
       </c>
-      <c r="L38" s="46">
+      <c r="L38" s="47">
         <f>L17+SUM(L19:L37)</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="B39" s="40" t="inlineStr">
+    <row r="39" ht="12.5" customHeight="1">
+      <c r="B39" s="41" t="inlineStr">
         <is>
           <t>VIN:</t>
         </is>
       </c>
-      <c r="C39" s="41" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="47" t="inlineStr">
-        <is>
-          <t>(Trade Vehicle 1)</t>
-        </is>
-      </c>
-      <c r="F39" s="43" t="inlineStr">
+      <c r="C39" s="42" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="48" t="inlineStr">
         <is>
           <t>Odometer:</t>
         </is>
       </c>
-      <c r="G39" s="41" t="n"/>
-      <c r="H39" s="48" t="inlineStr">
-        <is>
-          <t>☐ Not Accurate</t>
-        </is>
-      </c>
+      <c r="F39" s="42" t="n"/>
+      <c r="G39" s="48" t="inlineStr">
+        <is>
+          <t>☐ Not Accurate        (Trade Vehicle 1)</t>
+        </is>
+      </c>
+      <c r="H39" s="31" t="n"/>
       <c r="I39" s="9" t="n"/>
-      <c r="K39" s="31" t="inlineStr">
+      <c r="K39" s="32" t="inlineStr">
         <is>
           <t>LESS: TRADE IN ALLOWANCE</t>
         </is>
       </c>
-      <c r="L39" s="32" t="n"/>
-    </row>
-    <row r="40" ht="13" customHeight="1">
-      <c r="B40" s="40" t="inlineStr">
+      <c r="L39" s="33" t="n"/>
+    </row>
+    <row r="40" ht="12.5" customHeight="1">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>Trade Allowance:</t>
         </is>
       </c>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="43" t="inlineStr">
+      <c r="C40" s="31" t="n"/>
+      <c r="D40" s="49" t="n"/>
+      <c r="E40" s="44" t="inlineStr">
         <is>
           <t>Balance Owed to Lienholder:</t>
         </is>
       </c>
-      <c r="E40" s="30" t="n"/>
-      <c r="F40" s="49" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="30" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="K40" s="45" t="inlineStr">
+      <c r="F40" s="31" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="49" t="n"/>
+      <c r="I40" s="43" t="n"/>
+      <c r="K40" s="46" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="L40" s="46">
+      <c r="L40" s="47">
         <f>L38-L39</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="13" customHeight="1">
-      <c r="B41" s="40" t="inlineStr">
+    <row r="41" ht="12.5" customHeight="1">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>Lienholder Name:</t>
         </is>
       </c>
-      <c r="C41" s="41" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-      <c r="G41" s="10" t="n"/>
-      <c r="H41" s="10" t="n"/>
-      <c r="I41" s="42" t="n"/>
-      <c r="K41" s="31" t="inlineStr">
+      <c r="C41" s="31" t="n"/>
+      <c r="D41" s="42" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="43" t="n"/>
+      <c r="K41" s="32" t="inlineStr">
         <is>
           <t>SALES TAX</t>
         </is>
       </c>
-      <c r="L41" s="32" t="n"/>
-    </row>
-    <row r="42" ht="13" customHeight="1">
-      <c r="B42" s="40" t="inlineStr">
+      <c r="L41" s="33" t="n"/>
+    </row>
+    <row r="42" ht="12.5" customHeight="1">
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>Lienholder Address:</t>
         </is>
       </c>
-      <c r="C42" s="41" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="42" t="n"/>
-      <c r="K42" s="31" t="inlineStr">
+      <c r="C42" s="31" t="n"/>
+      <c r="D42" s="42" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="43" t="n"/>
+      <c r="K42" s="32" t="inlineStr">
         <is>
           <t>DEALER'S INVENTORY TAX</t>
         </is>
       </c>
-      <c r="L42" s="32" t="n"/>
-    </row>
-    <row r="43" ht="13" customHeight="1">
-      <c r="B43" s="40" t="inlineStr">
+      <c r="L42" s="33" t="n"/>
+    </row>
+    <row r="43" ht="12.5" customHeight="1">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>Year:</t>
         </is>
       </c>
-      <c r="C43" s="41" t="n"/>
-      <c r="D43" s="43" t="inlineStr">
+      <c r="C43" s="42" t="n"/>
+      <c r="D43" s="44" t="inlineStr">
         <is>
           <t>Make:</t>
         </is>
       </c>
-      <c r="E43" s="41" t="n"/>
-      <c r="F43" s="43" t="inlineStr">
+      <c r="E43" s="42" t="n"/>
+      <c r="F43" s="44" t="inlineStr">
         <is>
           <t>Model:</t>
         </is>
       </c>
-      <c r="G43" s="41" t="n"/>
-      <c r="H43" s="43" t="inlineStr">
+      <c r="G43" s="42" t="n"/>
+      <c r="H43" s="44" t="inlineStr">
         <is>
           <t>Color:</t>
         </is>
       </c>
-      <c r="I43" s="44" t="n"/>
-      <c r="K43" s="31" t="inlineStr">
+      <c r="I43" s="45" t="n"/>
+      <c r="K43" s="32" t="inlineStr">
         <is>
           <t>DOCUMENTARY FEE*</t>
         </is>
       </c>
-      <c r="L43" s="32" t="n"/>
-    </row>
-    <row r="44" ht="13" customHeight="1">
-      <c r="B44" s="40" t="inlineStr">
+      <c r="L43" s="33" t="n"/>
+    </row>
+    <row r="44" ht="12.5" customHeight="1">
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>VIN:</t>
         </is>
       </c>
-      <c r="C44" s="41" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="47" t="inlineStr">
-        <is>
-          <t>(Trade Vehicle 2)</t>
-        </is>
-      </c>
-      <c r="F44" s="43" t="inlineStr">
+      <c r="C44" s="42" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="48" t="inlineStr">
         <is>
           <t>Odometer:</t>
         </is>
       </c>
-      <c r="G44" s="41" t="n"/>
-      <c r="H44" s="48" t="inlineStr">
-        <is>
-          <t>☐ Not Accurate</t>
-        </is>
-      </c>
+      <c r="F44" s="42" t="n"/>
+      <c r="G44" s="48" t="inlineStr">
+        <is>
+          <t>☐ Not Accurate        (Trade Vehicle 2)</t>
+        </is>
+      </c>
+      <c r="H44" s="31" t="n"/>
       <c r="I44" s="9" t="n"/>
-      <c r="K44" s="31" t="inlineStr">
+      <c r="K44" s="32" t="inlineStr">
         <is>
           <t>STATE INSPECTION FEE</t>
         </is>
       </c>
-      <c r="L44" s="32" t="n"/>
-    </row>
-    <row r="45" ht="13" customHeight="1">
+      <c r="L44" s="33" t="n"/>
+    </row>
+    <row r="45" ht="12.5" customHeight="1">
       <c r="B45" s="50" t="inlineStr">
         <is>
           <t>Trade Allowance:</t>
         </is>
       </c>
-      <c r="C45" s="49" t="n"/>
-      <c r="D45" s="51" t="inlineStr">
+      <c r="C45" s="34" t="n"/>
+      <c r="D45" s="49" t="n"/>
+      <c r="E45" s="51" t="inlineStr">
         <is>
           <t>Balance Owed to Lienholder:</t>
         </is>
       </c>
-      <c r="E45" s="33" t="n"/>
-      <c r="F45" s="49" t="n"/>
-      <c r="G45" s="10" t="n"/>
-      <c r="H45" s="33" t="n"/>
-      <c r="I45" s="12" t="n"/>
-      <c r="K45" s="31" t="inlineStr">
+      <c r="F45" s="34" t="n"/>
+      <c r="G45" s="34" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="43" t="n"/>
+      <c r="K45" s="32" t="inlineStr">
         <is>
           <t>DEPUTY SERVICE FEE</t>
         </is>
       </c>
-      <c r="L45" s="32" t="n"/>
+      <c r="L45" s="33" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="B46" s="52" t="inlineStr">
@@ -1645,19 +1651,19 @@
           <t>OTHER MATERIAL UNDERSTANDINGS AND INTEGRATED DOCUMENTS</t>
         </is>
       </c>
-      <c r="C46" s="20" t="n"/>
-      <c r="D46" s="20" t="n"/>
-      <c r="E46" s="20" t="n"/>
-      <c r="F46" s="20" t="n"/>
-      <c r="G46" s="20" t="n"/>
-      <c r="H46" s="20" t="n"/>
-      <c r="I46" s="17" t="n"/>
-      <c r="K46" s="31" t="inlineStr">
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="21" t="n"/>
+      <c r="I46" s="18" t="n"/>
+      <c r="K46" s="32" t="inlineStr">
         <is>
           <t>LICENSE FEE</t>
         </is>
       </c>
-      <c r="L46" s="32" t="n"/>
+      <c r="L46" s="33" t="n"/>
     </row>
     <row r="47" ht="13" customHeight="1">
       <c r="B47" s="53" t="inlineStr">
@@ -1665,19 +1671,19 @@
           <t>☐  PLEASE SEE THE DELIVERY CONFIRMATION</t>
         </is>
       </c>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="27" t="n"/>
-      <c r="I47" s="7" t="n"/>
-      <c r="K47" s="31" t="inlineStr">
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="K47" s="32" t="inlineStr">
         <is>
           <t>TITLE FEE</t>
         </is>
       </c>
-      <c r="L47" s="32" t="n"/>
+      <c r="L47" s="33" t="n"/>
     </row>
     <row r="48" ht="13" customHeight="1">
       <c r="B48" s="54" t="inlineStr">
@@ -1685,19 +1691,19 @@
           <t>☐  PLEASE SEE THE CONDITIONAL DELIVERY AGREEMENT</t>
         </is>
       </c>
-      <c r="C48" s="30" t="n"/>
-      <c r="D48" s="30" t="n"/>
-      <c r="E48" s="30" t="n"/>
-      <c r="F48" s="30" t="n"/>
-      <c r="G48" s="30" t="n"/>
-      <c r="H48" s="30" t="n"/>
+      <c r="C48" s="31" t="n"/>
+      <c r="D48" s="31" t="n"/>
+      <c r="E48" s="31" t="n"/>
+      <c r="F48" s="31" t="n"/>
+      <c r="G48" s="31" t="n"/>
+      <c r="H48" s="31" t="n"/>
       <c r="I48" s="9" t="n"/>
-      <c r="K48" s="31" t="inlineStr">
+      <c r="K48" s="32" t="inlineStr">
         <is>
           <t>City Road &amp; Bridge</t>
         </is>
       </c>
-      <c r="L48" s="32" t="n"/>
+      <c r="L48" s="33" t="n"/>
     </row>
     <row r="49" ht="13" customHeight="1">
       <c r="B49" s="55" t="inlineStr">
@@ -1705,19 +1711,19 @@
           <t>Prospective Lienholder:</t>
         </is>
       </c>
-      <c r="C49" s="33" t="n"/>
-      <c r="D49" s="41" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
-      <c r="I49" s="42" t="n"/>
-      <c r="K49" s="31" t="inlineStr">
+      <c r="C49" s="34" t="n"/>
+      <c r="D49" s="42" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="11" t="n"/>
+      <c r="I49" s="43" t="n"/>
+      <c r="K49" s="32" t="inlineStr">
         <is>
           <t>Processing Fee</t>
         </is>
       </c>
-      <c r="L49" s="32" t="n"/>
+      <c r="L49" s="33" t="n"/>
     </row>
     <row r="50" ht="11" customHeight="1">
       <c r="B50" s="56" t="inlineStr">
@@ -1725,32 +1731,32 @@
           <t>Dealer's Inventory Tax: The Dealer's Inventory Tax charge is intended to reimburse the Dealer for ad valorem taxes on its motor vehicle inventory. The charge, which is paid by the Dealer to the county tax assessor-collector, is not a tax imposed on a consumer by the government, and is not required to be charged to the consumer.</t>
         </is>
       </c>
-      <c r="K50" s="31" t="inlineStr">
+      <c r="K50" s="32" t="inlineStr">
         <is>
           <t>Govt Vehicle Inspection Replacement Fee</t>
         </is>
       </c>
-      <c r="L50" s="32" t="n"/>
+      <c r="L50" s="33" t="n"/>
     </row>
     <row r="51" ht="11" customHeight="1"/>
     <row r="52" ht="11" customHeight="1">
-      <c r="K52" s="45" t="inlineStr">
+      <c r="K52" s="46" t="inlineStr">
         <is>
           <t>TOTAL DUE</t>
         </is>
       </c>
-      <c r="L52" s="46">
+      <c r="L52" s="47">
         <f>L40+SUM(L41:L50)</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="11" customHeight="1">
-      <c r="K53" s="31" t="inlineStr">
+      <c r="K53" s="32" t="inlineStr">
         <is>
           <t>DOWN PAYMENT</t>
         </is>
       </c>
-      <c r="L53" s="32" t="n"/>
+      <c r="L53" s="33" t="n"/>
     </row>
     <row r="54" ht="11" customHeight="1">
       <c r="B54" s="56" t="inlineStr">
@@ -1758,178 +1764,184 @@
           <t>*Documentary Fee: A documentary fee is not an official fee. A documentary fee is not required by law, but may be charged to buyers for handling documents relating to the sale. A documentary fee may not exceed a reasonable amount agreed to by the parties. This notice is required by law.  Traducción española: Vea Párrafo 13.</t>
         </is>
       </c>
-      <c r="K54" s="31" t="inlineStr">
+      <c r="K54" s="32" t="inlineStr">
         <is>
           <t>REBATES</t>
         </is>
       </c>
-      <c r="L54" s="32" t="n"/>
+      <c r="L54" s="33" t="n"/>
     </row>
     <row r="55" ht="11" customHeight="1">
-      <c r="K55" s="31" t="inlineStr">
+      <c r="K55" s="32" t="inlineStr">
         <is>
           <t>LESS CASH DUE AT DELIVERY</t>
         </is>
       </c>
-      <c r="L55" s="32" t="n"/>
+      <c r="L55" s="33" t="n"/>
     </row>
     <row r="56" ht="11" customHeight="1"/>
     <row r="57" ht="11" customHeight="1">
-      <c r="K57" s="45" t="inlineStr">
+      <c r="K57" s="46" t="inlineStr">
         <is>
           <t>AMOUNT TO BE FINANCED</t>
         </is>
       </c>
-      <c r="L57" s="46">
+      <c r="L57" s="47">
         <f>L52-L53-L54-L55</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="8" customHeight="1"/>
+    <row r="58" ht="7" customHeight="1"/>
     <row r="59" ht="24" customHeight="1">
       <c r="B59" s="57" t="inlineStr">
         <is>
           <t>Customer Approval:</t>
         </is>
       </c>
-      <c r="C59" s="27" t="n"/>
+      <c r="C59" s="28" t="n"/>
       <c r="D59" s="58" t="n"/>
-      <c r="E59" s="38" t="n"/>
-      <c r="F59" s="38" t="n"/>
+      <c r="E59" s="39" t="n"/>
+      <c r="F59" s="39" t="n"/>
       <c r="G59" s="59" t="inlineStr">
         <is>
           <t>Management Approval:</t>
         </is>
       </c>
-      <c r="H59" s="27" t="n"/>
-      <c r="I59" s="58" t="n"/>
-      <c r="J59" s="38" t="n"/>
-      <c r="K59" s="38" t="n"/>
-      <c r="L59" s="39" t="n"/>
-    </row>
-    <row r="60" ht="10" customHeight="1">
+      <c r="H59" s="28" t="n"/>
+      <c r="I59" s="28" t="n"/>
+      <c r="J59" s="58" t="n"/>
+      <c r="K59" s="39" t="n"/>
+      <c r="L59" s="40" t="n"/>
+    </row>
+    <row r="60" ht="9" customHeight="1">
       <c r="B60" s="60" t="inlineStr">
         <is>
           <t>By signing this authorization form, you certify that the above personal information is correct and accurate, and authorize the release of credit and employment information. By signing above, I provide to the dealership and its affiliates consent to communicate with me about my vehicle or any future vehicles using electronic verbal and written communications including but not limited to email, text messaging, SMS, phone calls and direct mail. Terms and conditions subject to credit approval. For information only. This is not an offer or contract for sale.</t>
         </is>
       </c>
-      <c r="C60" s="30" t="n"/>
-      <c r="D60" s="30" t="n"/>
-      <c r="E60" s="30" t="n"/>
-      <c r="F60" s="30" t="n"/>
-      <c r="G60" s="30" t="n"/>
-      <c r="H60" s="30" t="n"/>
-      <c r="I60" s="30" t="n"/>
-      <c r="J60" s="30" t="n"/>
-      <c r="K60" s="30" t="n"/>
+      <c r="C60" s="31" t="n"/>
+      <c r="D60" s="31" t="n"/>
+      <c r="E60" s="31" t="n"/>
+      <c r="F60" s="31" t="n"/>
+      <c r="G60" s="31" t="n"/>
+      <c r="H60" s="31" t="n"/>
+      <c r="I60" s="31" t="n"/>
+      <c r="J60" s="31" t="n"/>
+      <c r="K60" s="31" t="n"/>
       <c r="L60" s="9" t="n"/>
     </row>
-    <row r="61" ht="10" customHeight="1">
+    <row r="61" ht="9" customHeight="1">
       <c r="B61" s="8" t="n"/>
-      <c r="C61" s="30" t="n"/>
-      <c r="D61" s="30" t="n"/>
-      <c r="E61" s="30" t="n"/>
-      <c r="F61" s="30" t="n"/>
-      <c r="G61" s="30" t="n"/>
-      <c r="H61" s="30" t="n"/>
-      <c r="I61" s="30" t="n"/>
-      <c r="J61" s="30" t="n"/>
-      <c r="K61" s="30" t="n"/>
+      <c r="C61" s="31" t="n"/>
+      <c r="D61" s="31" t="n"/>
+      <c r="E61" s="31" t="n"/>
+      <c r="F61" s="31" t="n"/>
+      <c r="G61" s="31" t="n"/>
+      <c r="H61" s="31" t="n"/>
+      <c r="I61" s="31" t="n"/>
+      <c r="J61" s="31" t="n"/>
+      <c r="K61" s="31" t="n"/>
       <c r="L61" s="9" t="n"/>
     </row>
-    <row r="62" ht="10" customHeight="1">
+    <row r="62" ht="9" customHeight="1">
       <c r="B62" s="8" t="n"/>
-      <c r="C62" s="30" t="n"/>
-      <c r="D62" s="30" t="n"/>
-      <c r="E62" s="30" t="n"/>
-      <c r="F62" s="30" t="n"/>
-      <c r="G62" s="30" t="n"/>
-      <c r="H62" s="30" t="n"/>
-      <c r="I62" s="30" t="n"/>
-      <c r="J62" s="30" t="n"/>
-      <c r="K62" s="30" t="n"/>
+      <c r="C62" s="31" t="n"/>
+      <c r="D62" s="31" t="n"/>
+      <c r="E62" s="31" t="n"/>
+      <c r="F62" s="31" t="n"/>
+      <c r="G62" s="31" t="n"/>
+      <c r="H62" s="31" t="n"/>
+      <c r="I62" s="31" t="n"/>
+      <c r="J62" s="31" t="n"/>
+      <c r="K62" s="31" t="n"/>
       <c r="L62" s="9" t="n"/>
     </row>
-    <row r="63" ht="10" customHeight="1">
-      <c r="B63" s="11" t="n"/>
-      <c r="C63" s="33" t="n"/>
-      <c r="D63" s="33" t="n"/>
-      <c r="E63" s="33" t="n"/>
-      <c r="F63" s="33" t="n"/>
-      <c r="G63" s="33" t="n"/>
-      <c r="H63" s="33" t="n"/>
-      <c r="I63" s="33" t="n"/>
-      <c r="J63" s="33" t="n"/>
-      <c r="K63" s="33" t="n"/>
-      <c r="L63" s="12" t="n"/>
+    <row r="63" ht="9" customHeight="1">
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="34" t="n"/>
+      <c r="D63" s="34" t="n"/>
+      <c r="E63" s="34" t="n"/>
+      <c r="F63" s="34" t="n"/>
+      <c r="G63" s="34" t="n"/>
+      <c r="H63" s="34" t="n"/>
+      <c r="I63" s="34" t="n"/>
+      <c r="J63" s="34" t="n"/>
+      <c r="K63" s="34" t="n"/>
+      <c r="L63" s="13" t="n"/>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="B64" s="1" t="inlineStr">
+      <c r="B64" s="61" t="inlineStr">
         <is>
           <t>IMPORTANT TERMS AND CONDITIONS FOLLOW</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="C36:I36"/>
+  <mergeCells count="66">
+    <mergeCell ref="B4:F4"/>
     <mergeCell ref="D49:I49"/>
-    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="G1:L2"/>
     <mergeCell ref="B18:I25"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="B47:I47"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="E40:G40"/>
     <mergeCell ref="B32:I34"/>
     <mergeCell ref="E14:F14"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="F40:G40"/>
     <mergeCell ref="B46:I46"/>
-    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="G15:I15"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="I59:L59"/>
-    <mergeCell ref="H39:I39"/>
     <mergeCell ref="B60:L63"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="G14:I14"/>
-    <mergeCell ref="B4:E4"/>
     <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="E45:G45"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="D37:I37"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="C44:D44"/>
-    <mergeCell ref="B3:E3"/>
     <mergeCell ref="B27:I31"/>
-    <mergeCell ref="C42:I42"/>
+    <mergeCell ref="B1:F1"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B64:G64"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D42:I42"/>
+    <mergeCell ref="G44:I44"/>
     <mergeCell ref="E15:F15"/>
-    <mergeCell ref="F1:J2"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B10:L10"/>
     <mergeCell ref="B54:I57"/>
-    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="D59:F59"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D9:H9"/>
-    <mergeCell ref="C41:I41"/>
+    <mergeCell ref="G59:I59"/>
     <mergeCell ref="I3:J9"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B1:E1"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B50:I53"/>
-    <mergeCell ref="B64:F64"/>
     <mergeCell ref="E16:I16"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="J59:L59"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:I36"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B35:I35"/>
     <mergeCell ref="B26:I26"/>
   </mergeCells>
@@ -1954,436 +1966,436 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="61" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>RETAIL PURCHASE AGREEMENT</t>
         </is>
       </c>
-      <c r="B1" s="62" t="inlineStr">
+      <c r="B1" s="63" t="inlineStr">
         <is>
           <t>空白フォーム / Blank form - 記入ガイド (A4 1ページ)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="63" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>入力欄 (Input)</t>
         </is>
       </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" s="65" t="inlineStr">
         <is>
           <t>説明</t>
         </is>
       </c>
-      <c r="C3" s="63" t="inlineStr">
+      <c r="C3" s="64" t="inlineStr">
         <is>
           <t>記入例 (Example)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="65" t="inlineStr">
-        <is>
-          <t>B1:E4</t>
-        </is>
-      </c>
-      <c r="B4" s="66" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
+        <is>
+          <t>B1:F4</t>
+        </is>
+      </c>
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>ディーラー名・住所・Tel / Fax</t>
         </is>
       </c>
-      <c r="C4" s="65" t="inlineStr">
+      <c r="C4" s="66" t="inlineStr">
         <is>
           <t>EXCELLENT AUTO SALES...</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="66" t="inlineStr">
         <is>
           <t>I3:J9</t>
         </is>
       </c>
-      <c r="B5" s="66" t="inlineStr">
+      <c r="B5" s="67" t="inlineStr">
         <is>
           <t>自動車メーカーのエンブレム枠 (画像を差し替え)</t>
         </is>
       </c>
-      <c r="C5" s="65" t="inlineStr">
+      <c r="C5" s="66" t="inlineStr">
         <is>
           <t>日産エンブレム(サンプル)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="65" t="inlineStr">
-        <is>
-          <t>L1 / L2</t>
-        </is>
-      </c>
-      <c r="B6" s="66" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
+        <is>
+          <t>L3 / L4</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>CUST# / Deal Number</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>408132 / 343179</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="66" t="inlineStr">
         <is>
           <t>D6:H6 / L6</t>
         </is>
       </c>
-      <c r="B7" s="66" t="inlineStr">
+      <c r="B7" s="67" t="inlineStr">
         <is>
           <t>Purchaser's Name(s) / Date</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="66" t="inlineStr">
         <is>
           <t>JOHN DOE / 08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="65" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>D7:H7 / L7</t>
         </is>
       </c>
-      <c r="B8" s="66" t="inlineStr">
+      <c r="B8" s="67" t="inlineStr">
         <is>
           <t>Address(es) / County</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="C8" s="66" t="inlineStr">
         <is>
           <t>541 RUBY RIVER DR / MADISON</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="66" t="inlineStr">
         <is>
           <t>D8:H8 / L8</t>
         </is>
       </c>
-      <c r="B9" s="66" t="inlineStr">
+      <c r="B9" s="67" t="inlineStr">
         <is>
           <t>Telephone (1) / Telephone (2)</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="66" t="inlineStr">
         <is>
           <t>555-0100 / N/A</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>D9:H9 / L9</t>
         </is>
       </c>
-      <c r="B10" s="66" t="inlineStr">
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>Email (1) / Email (2)</t>
         </is>
       </c>
-      <c r="C10" s="65" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>sample@example.com</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="inlineStr">
+      <c r="A11" s="66" t="inlineStr">
         <is>
           <t>B13:I13</t>
         </is>
       </c>
-      <c r="B11" s="66" t="inlineStr">
+      <c r="B11" s="67" t="inlineStr">
         <is>
           <t>YEAR / MAKE / MODEL / COLOR / STOCK NO.</t>
         </is>
       </c>
-      <c r="C11" s="65" t="inlineStr">
+      <c r="C11" s="66" t="inlineStr">
         <is>
           <t>2026 / FORD / BRONCO</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="65" t="inlineStr">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t>B15:I15</t>
         </is>
       </c>
-      <c r="B12" s="66" t="inlineStr">
+      <c r="B12" s="67" t="inlineStr">
         <is>
           <t>VIN / ODOMETER READING / SALESPERSON</t>
         </is>
       </c>
-      <c r="C12" s="65" t="inlineStr">
+      <c r="C12" s="66" t="inlineStr">
         <is>
           <t>1FMEE4DP3TLB00730 / 11</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="A13" s="66" t="inlineStr">
         <is>
           <t>B16:I16</t>
         </is>
       </c>
-      <c r="B13" s="66" t="inlineStr">
+      <c r="B13" s="67" t="inlineStr">
         <is>
           <t>New・Used、Prior Use Disclosure のチェック欄 (☐ を ☑ に置換)</t>
         </is>
       </c>
-      <c r="C13" s="65" t="inlineStr">
+      <c r="C13" s="66" t="inlineStr">
         <is>
           <t>☑ NEW</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="65" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>C36:I45</t>
         </is>
       </c>
-      <c r="B14" s="66" t="inlineStr">
+      <c r="B14" s="67" t="inlineStr">
         <is>
           <t>TRADE VEHICLE INFORMATION (下取車 1・2)</t>
         </is>
       </c>
-      <c r="C14" s="65" t="inlineStr">
+      <c r="C14" s="66" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="65" t="inlineStr">
+      <c r="A15" s="66" t="inlineStr">
         <is>
           <t>D49</t>
         </is>
       </c>
-      <c r="B15" s="66" t="inlineStr">
+      <c r="B15" s="67" t="inlineStr">
         <is>
           <t>Prospective Lienholder</t>
         </is>
       </c>
-      <c r="C15" s="65" t="inlineStr">
+      <c r="C15" s="66" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="65" t="inlineStr">
+      <c r="A16" s="66" t="inlineStr">
         <is>
           <t>L17</t>
         </is>
       </c>
-      <c r="B16" s="66" t="inlineStr">
+      <c r="B16" s="67" t="inlineStr">
         <is>
           <t>Base Selling Price</t>
         </is>
       </c>
-      <c r="C16" s="65" t="inlineStr">
+      <c r="C16" s="66" t="inlineStr">
         <is>
           <t>$52,810.00</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="65" t="inlineStr">
+      <c r="A17" s="66" t="inlineStr">
         <is>
           <t>K19:L37</t>
         </is>
       </c>
-      <c r="B17" s="66" t="inlineStr">
+      <c r="B17" s="67" t="inlineStr">
         <is>
           <t>Optional Items - 品名を K 列、金額を L 列に入力</t>
         </is>
       </c>
-      <c r="C17" s="65" t="inlineStr">
+      <c r="C17" s="66" t="inlineStr">
         <is>
           <t>ALARM-AT / $305.00</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="65" t="inlineStr">
+      <c r="A18" s="66" t="inlineStr">
         <is>
           <t>L39</t>
         </is>
       </c>
-      <c r="B18" s="66" t="inlineStr">
+      <c r="B18" s="67" t="inlineStr">
         <is>
           <t>LESS: TRADE IN ALLOWANCE</t>
         </is>
       </c>
-      <c r="C18" s="65" t="inlineStr">
+      <c r="C18" s="66" t="inlineStr">
         <is>
           <t>$0.00</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="65" t="inlineStr">
+      <c r="A19" s="66" t="inlineStr">
         <is>
           <t>L41:L50</t>
         </is>
       </c>
-      <c r="B19" s="66" t="inlineStr">
+      <c r="B19" s="67" t="inlineStr">
         <is>
           <t>各種税金・手数料 (SALES TAX 〜 Govt Vehicle Inspection Replacement Fee)</t>
         </is>
       </c>
-      <c r="C19" s="65" t="inlineStr">
+      <c r="C19" s="66" t="inlineStr">
         <is>
           <t>$225.00</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="65" t="inlineStr">
+      <c r="A20" s="66" t="inlineStr">
         <is>
           <t>L53 / L54 / L55</t>
         </is>
       </c>
-      <c r="B20" s="66" t="inlineStr">
+      <c r="B20" s="67" t="inlineStr">
         <is>
           <t>DOWN PAYMENT / REBATES / LESS CASH DUE AT DELIVERY</t>
         </is>
       </c>
-      <c r="C20" s="65" t="inlineStr">
+      <c r="C20" s="66" t="inlineStr">
         <is>
           <t>$0.00 / $2,000.00 / $0.00</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="65" t="inlineStr">
-        <is>
-          <t>D59 / I59</t>
-        </is>
-      </c>
-      <c r="B21" s="66" t="inlineStr">
+      <c r="A21" s="66" t="inlineStr">
+        <is>
+          <t>D59 / J59</t>
+        </is>
+      </c>
+      <c r="B21" s="67" t="inlineStr">
         <is>
           <t>Customer Approval / Management Approval (署名欄)</t>
         </is>
       </c>
-      <c r="C21" s="65" t="inlineStr">
+      <c r="C21" s="66" t="inlineStr">
         <is>
           <t>署名</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="63" t="inlineStr">
+      <c r="A23" s="64" t="inlineStr">
         <is>
           <t>自動計算 (編集しないこと)</t>
         </is>
       </c>
-      <c r="B23" s="64" t="inlineStr">
+      <c r="B23" s="65" t="inlineStr">
         <is>
           <t>計算式</t>
         </is>
       </c>
-      <c r="C23" s="63" t="inlineStr"/>
+      <c r="C23" s="64" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="65" t="inlineStr">
+      <c r="A24" s="66" t="inlineStr">
         <is>
           <t>L38  TOTAL SELLING PRICE</t>
         </is>
       </c>
-      <c r="B24" s="66">
+      <c r="B24" s="67">
         <f> L17 + SUM(L19:L37)</f>
         <v/>
       </c>
-      <c r="C24" s="65" t="inlineStr"/>
+      <c r="C24" s="66" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="65" t="inlineStr">
+      <c r="A25" s="66" t="inlineStr">
         <is>
           <t>L40  SUBTOTAL</t>
         </is>
       </c>
-      <c r="B25" s="66">
+      <c r="B25" s="67">
         <f> L38 - L39</f>
         <v/>
       </c>
-      <c r="C25" s="65" t="inlineStr"/>
+      <c r="C25" s="66" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="65" t="inlineStr">
+      <c r="A26" s="66" t="inlineStr">
         <is>
           <t>L52  TOTAL DUE</t>
         </is>
       </c>
-      <c r="B26" s="66">
+      <c r="B26" s="67">
         <f> L40 + SUM(L41:L50)</f>
         <v/>
       </c>
-      <c r="C26" s="65" t="inlineStr"/>
+      <c r="C26" s="66" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="65" t="inlineStr">
+      <c r="A27" s="66" t="inlineStr">
         <is>
           <t>L57  AMOUNT TO BE FINANCED</t>
         </is>
       </c>
-      <c r="B27" s="66">
+      <c r="B27" s="67">
         <f> L52 - L53 - L54 - L55</f>
         <v/>
       </c>
-      <c r="C27" s="65" t="inlineStr"/>
+      <c r="C27" s="66" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="65" t="inlineStr"/>
-      <c r="B29" s="66" t="inlineStr">
+      <c r="A29" s="66" t="inlineStr"/>
+      <c r="B29" s="67" t="inlineStr">
         <is>
           <t>・用紙は A4 縦・1ページに収まるよう設定済み (余白 上下 0.2" / 左右 0.22")。そのまま印刷してください。</t>
         </is>
       </c>
-      <c r="C29" s="65" t="inlineStr"/>
+      <c r="C29" s="66" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="65" t="inlineStr"/>
-      <c r="B30" s="66" t="inlineStr">
+      <c r="A30" s="66" t="inlineStr"/>
+      <c r="B30" s="67" t="inlineStr">
         <is>
           <t>・金額欄の書式は $#,##0.00 (USD)。マイナスは ($#,##0.00)、空欄は「-」と表示されます。</t>
         </is>
       </c>
-      <c r="C30" s="65" t="inlineStr"/>
+      <c r="C30" s="66" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="65" t="inlineStr"/>
-      <c r="B31" s="66" t="inlineStr">
+      <c r="A31" s="66" t="inlineStr"/>
+      <c r="B31" s="67" t="inlineStr">
         <is>
           <t>・グレー網掛けの行は数式です。上書きすると再計算されません。</t>
         </is>
       </c>
-      <c r="C31" s="65" t="inlineStr"/>
+      <c r="C31" s="66" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="65" t="inlineStr"/>
-      <c r="B32" s="66" t="inlineStr">
+      <c r="A32" s="66" t="inlineStr"/>
+      <c r="B32" s="67" t="inlineStr">
         <is>
           <t>・エンブレムは I3:J9 の枠内に画像として配置しています。差し替えは画像を選択して削除し、[挿入]→[画像] で同じ枠に貼り直してください。サンプルの日産エンブレムは簡易的な代替図形です。</t>
         </is>
       </c>
-      <c r="C32" s="65" t="inlineStr"/>
+      <c r="C32" s="66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Retail_Purchase_Agreement_Blank.xlsx
+++ b/Retail_Purchase_Agreement_Blank.xlsx
@@ -578,11 +578,11 @@
   <oneCellAnchor>
     <from>
       <col>8</col>
-      <colOff>38100</colOff>
-      <row>2</row>
-      <rowOff>209550</rowOff>
+      <colOff>19050</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1095375" cy="809625"/>
+    <ext cx="1123950" cy="419100"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C5" s="66" t="inlineStr">
         <is>
-          <t>日産エンブレム(サンプル)</t>
+          <t>Ford エンブレム</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       <c r="A32" s="66" t="inlineStr"/>
       <c r="B32" s="67" t="inlineStr">
         <is>
-          <t>・エンブレムは I3:J9 の枠内に画像として配置しています。差し替えは画像を選択して削除し、[挿入]→[画像] で同じ枠に貼り直してください。サンプルの日産エンブレムは簡易的な代替図形です。</t>
+          <t>・エンブレムは I3:J9 の枠内に画像として配置しています。差し替えは画像を選択して削除し、[挿入]→[画像] で同じ枠に貼り直してください。</t>
         </is>
       </c>
       <c r="C32" s="66" t="inlineStr"/>
